--- a/Team-Data/2008-09/12-16-2008-09.xlsx
+++ b/Team-Data/2008-09/12-16-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,22 +806,22 @@
         <v>1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF2" t="n">
         <v>8</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AH2" t="n">
         <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ2" t="n">
         <v>25</v>
@@ -769,13 +836,13 @@
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
         <v>25</v>
@@ -790,25 +857,25 @@
         <v>21</v>
       </c>
       <c r="AU2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AV2" t="n">
         <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX2" t="n">
         <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
         <v>6</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB2" t="n">
         <v>23</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -843,85 +910,85 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.917</v>
+        <v>0.92</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="J3" t="n">
-        <v>75.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="L3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M3" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.368</v>
+        <v>0.362</v>
       </c>
       <c r="O3" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="P3" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.764</v>
+        <v>0.758</v>
       </c>
       <c r="R3" t="n">
         <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>33</v>
+        <v>32.8</v>
       </c>
       <c r="T3" t="n">
-        <v>43.8</v>
+        <v>43.5</v>
       </c>
       <c r="U3" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="V3" t="n">
         <v>16.2</v>
       </c>
       <c r="W3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="AA3" t="n">
         <v>24.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.3</v>
+        <v>100.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,13 +1003,13 @@
         <v>11</v>
       </c>
       <c r="AI3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ3" t="n">
         <v>29</v>
       </c>
       <c r="AK3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL3" t="n">
         <v>18</v>
@@ -951,28 +1018,28 @@
         <v>22</v>
       </c>
       <c r="AN3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO3" t="n">
         <v>2</v>
       </c>
       <c r="AP3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AR3" t="n">
         <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AU3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AV3" t="n">
         <v>28</v>
@@ -981,10 +1048,10 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
         <v>26</v>
@@ -993,10 +1060,10 @@
         <v>2</v>
       </c>
       <c r="BB3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -1025,88 +1092,88 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
         <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>0.308</v>
+        <v>0.28</v>
       </c>
       <c r="H4" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="I4" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="J4" t="n">
-        <v>75.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K4" t="n">
         <v>0.434</v>
       </c>
       <c r="L4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="M4" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0.353</v>
+        <v>0.349</v>
       </c>
       <c r="O4" t="n">
-        <v>19.2</v>
+        <v>18.7</v>
       </c>
       <c r="P4" t="n">
-        <v>25.7</v>
+        <v>25</v>
       </c>
       <c r="Q4" t="n">
         <v>0.748</v>
       </c>
       <c r="R4" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S4" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="T4" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="U4" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="V4" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W4" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.6</v>
+        <v>21.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>90</v>
+        <v>89.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.6</v>
+        <v>-4.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF4" t="n">
         <v>25</v>
@@ -1115,7 +1182,7 @@
         <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1124,22 +1191,22 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM4" t="n">
         <v>24</v>
       </c>
-      <c r="AM4" t="n">
-        <v>26</v>
-      </c>
       <c r="AN4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP4" t="n">
         <v>13</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>10</v>
       </c>
       <c r="AQ4" t="n">
         <v>24</v>
@@ -1157,28 +1224,28 @@
         <v>29</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -1210,103 +1277,103 @@
         <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>0.435</v>
+        <v>0.478</v>
       </c>
       <c r="H5" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="I5" t="n">
-        <v>37.2</v>
+        <v>36.9</v>
       </c>
       <c r="J5" t="n">
-        <v>84.8</v>
+        <v>83.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.438</v>
+        <v>0.44</v>
       </c>
       <c r="L5" t="n">
         <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.367</v>
+        <v>0.37</v>
       </c>
       <c r="O5" t="n">
-        <v>18.8</v>
+        <v>19.7</v>
       </c>
       <c r="P5" t="n">
-        <v>23.3</v>
+        <v>24.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="R5" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S5" t="n">
-        <v>31.2</v>
+        <v>30.8</v>
       </c>
       <c r="T5" t="n">
-        <v>42.9</v>
+        <v>42.7</v>
       </c>
       <c r="U5" t="n">
         <v>19.7</v>
       </c>
       <c r="V5" t="n">
-        <v>15.1</v>
+        <v>15.5</v>
       </c>
       <c r="W5" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>20</v>
+        <v>20.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>99</v>
+        <v>99.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.8</v>
+        <v>-1.9</v>
       </c>
       <c r="AD5" t="n">
         <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG5" t="n">
         <v>17</v>
       </c>
-      <c r="AG5" t="n">
-        <v>19</v>
-      </c>
       <c r="AH5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AI5" t="n">
         <v>10</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL5" t="n">
         <v>17</v>
@@ -1315,22 +1382,22 @@
         <v>21</v>
       </c>
       <c r="AN5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AP5" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
         <v>4</v>
       </c>
       <c r="AR5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1339,28 +1406,28 @@
         <v>23</v>
       </c>
       <c r="AV5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>20</v>
       </c>
-      <c r="AW5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>24</v>
-      </c>
       <c r="BA5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -1389,142 +1456,142 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" t="n">
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.87</v>
+        <v>0.833</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>38.3</v>
+        <v>37.9</v>
       </c>
       <c r="J6" t="n">
-        <v>80.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.478</v>
+        <v>0.476</v>
       </c>
       <c r="L6" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="N6" t="n">
-        <v>0.341</v>
+        <v>0.337</v>
       </c>
       <c r="O6" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="P6" t="n">
-        <v>25.4</v>
+        <v>25.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.785</v>
+        <v>0.782</v>
       </c>
       <c r="R6" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S6" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T6" t="n">
         <v>42.5</v>
       </c>
       <c r="U6" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="V6" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="W6" t="n">
         <v>7.9</v>
       </c>
       <c r="X6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>103.5</v>
+        <v>102.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.5</v>
+        <v>12.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
         <v>24</v>
       </c>
       <c r="AI6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK6" t="n">
         <v>4</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3</v>
-      </c>
       <c r="AL6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM6" t="n">
         <v>8</v>
       </c>
       <c r="AN6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO6" t="n">
         <v>8</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AQ6" t="n">
         <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
         <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="n">
         <v>5</v>
@@ -1533,13 +1600,13 @@
         <v>2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BB6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -1652,10 +1719,10 @@
         <v>22</v>
       </c>
       <c r="AE7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
         <v>14</v>
@@ -1664,10 +1731,10 @@
         <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AK7" t="n">
         <v>16</v>
@@ -1682,10 +1749,10 @@
         <v>24</v>
       </c>
       <c r="AO7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AQ7" t="n">
         <v>7</v>
@@ -1700,7 +1767,7 @@
         <v>2</v>
       </c>
       <c r="AU7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV7" t="n">
         <v>7</v>
@@ -1709,16 +1776,16 @@
         <v>17</v>
       </c>
       <c r="AX7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ7" t="n">
         <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
         <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>0.68</v>
+        <v>0.708</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
@@ -1771,85 +1838,85 @@
         <v>36.9</v>
       </c>
       <c r="J8" t="n">
-        <v>78.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="K8" t="n">
         <v>0.468</v>
       </c>
       <c r="L8" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M8" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.365</v>
+        <v>0.361</v>
       </c>
       <c r="O8" t="n">
-        <v>23.2</v>
+        <v>23.7</v>
       </c>
       <c r="P8" t="n">
-        <v>30.4</v>
+        <v>30.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.764</v>
+        <v>0.765</v>
       </c>
       <c r="R8" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>31.3</v>
+        <v>31.8</v>
       </c>
       <c r="T8" t="n">
-        <v>41.5</v>
+        <v>41.8</v>
       </c>
       <c r="U8" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="V8" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="X8" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="Y8" t="n">
         <v>6.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.4</v>
+        <v>103.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG8" t="n">
         <v>5</v>
       </c>
       <c r="AH8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
         <v>11</v>
       </c>
       <c r="AJ8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1858,7 +1925,7 @@
         <v>16</v>
       </c>
       <c r="AM8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN8" t="n">
         <v>15</v>
@@ -1870,43 +1937,43 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AS8" t="n">
         <v>9</v>
       </c>
       <c r="AT8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU8" t="n">
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX8" t="n">
         <v>3</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4</v>
       </c>
       <c r="AY8" t="n">
         <v>27</v>
       </c>
       <c r="AZ8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA8" t="n">
         <v>3</v>
       </c>
       <c r="BB8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2083,7 @@
         <v>28</v>
       </c>
       <c r="AE9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF9" t="n">
         <v>8</v>
@@ -2034,19 +2101,19 @@
         <v>22</v>
       </c>
       <c r="AK9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL9" t="n">
         <v>19</v>
       </c>
       <c r="AM9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN9" t="n">
         <v>6</v>
       </c>
       <c r="AO9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP9" t="n">
         <v>15</v>
@@ -2055,7 +2122,7 @@
         <v>16</v>
       </c>
       <c r="AR9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS9" t="n">
         <v>25</v>
@@ -2064,13 +2131,13 @@
         <v>26</v>
       </c>
       <c r="AU9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV9" t="n">
         <v>4</v>
       </c>
       <c r="AW9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
         <v>13</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -2195,34 +2262,34 @@
         <v>-5.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF10" t="n">
         <v>25</v>
       </c>
       <c r="AG10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK10" t="n">
         <v>19</v>
       </c>
       <c r="AL10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN10" t="n">
         <v>28</v>
@@ -2231,7 +2298,7 @@
         <v>3</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ10" t="n">
         <v>23</v>
@@ -2249,16 +2316,16 @@
         <v>21</v>
       </c>
       <c r="AV10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW10" t="n">
         <v>5</v>
       </c>
       <c r="AX10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ10" t="n">
         <v>12</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -2299,85 +2366,85 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.64</v>
+        <v>0.625</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>34.7</v>
+        <v>34.4</v>
       </c>
       <c r="J11" t="n">
-        <v>79.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="K11" t="n">
-        <v>0.436</v>
+        <v>0.431</v>
       </c>
       <c r="L11" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="M11" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.379</v>
+        <v>0.375</v>
       </c>
       <c r="O11" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="P11" t="n">
-        <v>25.2</v>
+        <v>25.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.819</v>
+        <v>0.821</v>
       </c>
       <c r="R11" t="n">
         <v>11</v>
       </c>
       <c r="S11" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="T11" t="n">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
       <c r="U11" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="V11" t="n">
         <v>13.8</v>
       </c>
       <c r="W11" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X11" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="Z11" t="n">
         <v>18.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>97.2</v>
+        <v>96.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE11" t="n">
         <v>6</v>
@@ -2389,31 +2456,31 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
         <v>29</v>
       </c>
       <c r="AJ11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK11" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AL11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AM11" t="n">
         <v>12</v>
       </c>
       <c r="AN11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AO11" t="n">
         <v>6</v>
       </c>
       <c r="AP11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ11" t="n">
         <v>2</v>
@@ -2422,10 +2489,10 @@
         <v>17</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AU11" t="n">
         <v>25</v>
@@ -2440,16 +2507,16 @@
         <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ11" t="n">
         <v>1</v>
       </c>
       <c r="BA11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC11" t="n">
         <v>8</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -2559,22 +2626,22 @@
         <v>-2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
         <v>23</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG12" t="n">
         <v>23</v>
       </c>
       <c r="AH12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ12" t="n">
         <v>3</v>
@@ -2583,7 +2650,7 @@
         <v>18</v>
       </c>
       <c r="AL12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM12" t="n">
         <v>9</v>
@@ -2592,7 +2659,7 @@
         <v>21</v>
       </c>
       <c r="AO12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP12" t="n">
         <v>27</v>
@@ -2616,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="AW12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX12" t="n">
         <v>12</v>
@@ -2628,13 +2695,13 @@
         <v>27</v>
       </c>
       <c r="BA12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -2663,34 +2730,34 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.292</v>
+        <v>0.261</v>
       </c>
       <c r="H13" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I13" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J13" t="n">
         <v>84.09999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L13" t="n">
         <v>5.3</v>
       </c>
       <c r="M13" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="N13" t="n">
         <v>0.315</v>
@@ -2699,10 +2766,10 @@
         <v>15.5</v>
       </c>
       <c r="P13" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.736</v>
+        <v>0.735</v>
       </c>
       <c r="R13" t="n">
         <v>12.2</v>
@@ -2711,7 +2778,7 @@
         <v>29.7</v>
       </c>
       <c r="T13" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U13" t="n">
         <v>20.1</v>
@@ -2720,10 +2787,10 @@
         <v>14.8</v>
       </c>
       <c r="W13" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="X13" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="Y13" t="n">
         <v>5</v>
@@ -2732,40 +2799,40 @@
         <v>21.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>-4.7</v>
+        <v>-5.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AE13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF13" t="n">
         <v>24</v>
       </c>
       <c r="AG13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AH13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM13" t="n">
         <v>20</v>
@@ -2789,19 +2856,19 @@
         <v>20</v>
       </c>
       <c r="AT13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU13" t="n">
         <v>20</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY13" t="n">
         <v>16</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -2860,10 +2927,10 @@
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>40.3</v>
+        <v>40</v>
       </c>
       <c r="J14" t="n">
-        <v>85.2</v>
+        <v>84.5</v>
       </c>
       <c r="K14" t="n">
         <v>0.473</v>
@@ -2872,34 +2939,34 @@
         <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.3</v>
+        <v>17.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.366</v>
+        <v>0.38</v>
       </c>
       <c r="O14" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="P14" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R14" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="S14" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
       <c r="T14" t="n">
         <v>46</v>
       </c>
       <c r="U14" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="V14" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W14" t="n">
         <v>9.6</v>
@@ -2914,13 +2981,13 @@
         <v>20</v>
       </c>
       <c r="AA14" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.9</v>
+        <v>108</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.9</v>
+        <v>10.7</v>
       </c>
       <c r="AD14" t="n">
         <v>22</v>
@@ -2941,19 +3008,19 @@
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK14" t="n">
         <v>5</v>
       </c>
       <c r="AL14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AM14" t="n">
         <v>14</v>
       </c>
-      <c r="AM14" t="n">
-        <v>13</v>
-      </c>
       <c r="AN14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2962,13 +3029,13 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR14" t="n">
         <v>5</v>
       </c>
       <c r="AS14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2977,13 +3044,13 @@
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY14" t="n">
         <v>6</v>
@@ -2998,7 +3065,7 @@
         <v>1</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -3027,160 +3094,160 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E15" t="n">
         <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>0.36</v>
+        <v>0.375</v>
       </c>
       <c r="H15" t="n">
         <v>48.2</v>
       </c>
       <c r="I15" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="J15" t="n">
-        <v>77.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L15" t="n">
         <v>4.8</v>
       </c>
       <c r="M15" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.345</v>
+        <v>0.35</v>
       </c>
       <c r="O15" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="P15" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R15" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="S15" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T15" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="U15" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="V15" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="W15" t="n">
         <v>7.6</v>
       </c>
       <c r="X15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y15" t="n">
         <v>4.4</v>
       </c>
-      <c r="Y15" t="n">
-        <v>4.6</v>
-      </c>
       <c r="Z15" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AA15" t="n">
         <v>21.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>94.8</v>
+        <v>95.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-3.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
         <v>22</v>
       </c>
       <c r="AF15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG15" t="n">
         <v>22</v>
       </c>
       <c r="AH15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ15" t="n">
         <v>26</v>
       </c>
       <c r="AK15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM15" t="n">
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO15" t="n">
         <v>14</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
         <v>17</v>
       </c>
       <c r="AR15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AS15" t="n">
         <v>26</v>
       </c>
       <c r="AT15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU15" t="n">
         <v>30</v>
       </c>
       <c r="AV15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
         <v>10</v>
       </c>
       <c r="AX15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA15" t="n">
         <v>10</v>
       </c>
       <c r="BB15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-0.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
         <v>15</v>
@@ -3299,7 +3366,7 @@
         <v>16</v>
       </c>
       <c r="AH16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI16" t="n">
         <v>16</v>
@@ -3311,25 +3378,25 @@
         <v>20</v>
       </c>
       <c r="AL16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AQ16" t="n">
         <v>28</v>
       </c>
       <c r="AR16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS16" t="n">
         <v>27</v>
@@ -3356,7 +3423,7 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB16" t="n">
         <v>20</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" t="n">
         <v>11</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>0.44</v>
+        <v>0.423</v>
       </c>
       <c r="H17" t="n">
         <v>48.6</v>
@@ -3409,10 +3476,10 @@
         <v>36</v>
       </c>
       <c r="J17" t="n">
-        <v>82.7</v>
+        <v>82.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L17" t="n">
         <v>5.2</v>
@@ -3421,34 +3488,34 @@
         <v>14.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.351</v>
+        <v>0.354</v>
       </c>
       <c r="O17" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="P17" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R17" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="S17" t="n">
-        <v>30.7</v>
+        <v>30.3</v>
       </c>
       <c r="T17" t="n">
-        <v>44.1</v>
+        <v>43.6</v>
       </c>
       <c r="U17" t="n">
         <v>20.6</v>
       </c>
       <c r="V17" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="W17" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="X17" t="n">
         <v>3.6</v>
@@ -3457,73 +3524,73 @@
         <v>5.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.5</v>
+        <v>-2</v>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AH17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL17" t="n">
         <v>23</v>
       </c>
       <c r="AM17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
         <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS17" t="n">
         <v>14</v>
       </c>
       <c r="AT17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU17" t="n">
         <v>19</v>
       </c>
       <c r="AV17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW17" t="n">
         <v>24</v>
@@ -3538,13 +3605,13 @@
         <v>30</v>
       </c>
       <c r="BA17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB17" t="n">
         <v>19</v>
       </c>
       <c r="BC17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-7.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
         <v>28</v>
@@ -3663,13 +3730,13 @@
         <v>29</v>
       </c>
       <c r="AH18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI18" t="n">
         <v>22</v>
       </c>
       <c r="AJ18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK18" t="n">
         <v>30</v>
@@ -3684,13 +3751,13 @@
         <v>25</v>
       </c>
       <c r="AO18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP18" t="n">
         <v>14</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR18" t="n">
         <v>6</v>
@@ -3702,10 +3769,10 @@
         <v>15</v>
       </c>
       <c r="AU18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW18" t="n">
         <v>29</v>
@@ -3714,16 +3781,16 @@
         <v>21</v>
       </c>
       <c r="AY18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ18" t="n">
         <v>25</v>
       </c>
       <c r="BA18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -3857,13 +3924,13 @@
         <v>21</v>
       </c>
       <c r="AL19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM19" t="n">
         <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO19" t="n">
         <v>5</v>
@@ -3872,7 +3939,7 @@
         <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR19" t="n">
         <v>13</v>
@@ -3893,7 +3960,7 @@
         <v>27</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
         <v>20</v>
@@ -3908,7 +3975,7 @@
         <v>11</v>
       </c>
       <c r="BC19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -3937,82 +4004,82 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F20" t="n">
         <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>0.667</v>
+        <v>0.65</v>
       </c>
       <c r="H20" t="n">
         <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>35</v>
+        <v>35.4</v>
       </c>
       <c r="J20" t="n">
-        <v>75.8</v>
+        <v>76.5</v>
       </c>
       <c r="K20" t="n">
-        <v>0.461</v>
+        <v>0.463</v>
       </c>
       <c r="L20" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M20" t="n">
         <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.412</v>
+        <v>0.407</v>
       </c>
       <c r="O20" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="P20" t="n">
-        <v>23.1</v>
+        <v>22.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="R20" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="S20" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="T20" t="n">
-        <v>38.6</v>
+        <v>39</v>
       </c>
       <c r="U20" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="V20" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W20" t="n">
         <v>8</v>
       </c>
       <c r="X20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Z20" t="n">
         <v>21.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.7</v>
+        <v>97</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AD20" t="n">
         <v>30</v>
@@ -4024,22 +4091,22 @@
         <v>5</v>
       </c>
       <c r="AG20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH20" t="n">
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK20" t="n">
         <v>8</v>
       </c>
       <c r="AL20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM20" t="n">
         <v>11</v>
@@ -4048,10 +4115,10 @@
         <v>1</v>
       </c>
       <c r="AO20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AP20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ20" t="n">
         <v>3</v>
@@ -4063,16 +4130,16 @@
         <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU20" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AV20" t="n">
         <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX20" t="n">
         <v>26</v>
@@ -4084,13 +4151,13 @@
         <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BC20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -4119,58 +4186,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E21" t="n">
         <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>0.44</v>
+        <v>0.458</v>
       </c>
       <c r="H21" t="n">
         <v>48.2</v>
       </c>
       <c r="I21" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J21" t="n">
-        <v>87.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L21" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="M21" t="n">
         <v>29.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.358</v>
+        <v>0.355</v>
       </c>
       <c r="O21" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="P21" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.806</v>
+        <v>0.797</v>
       </c>
       <c r="R21" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S21" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T21" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="U21" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="V21" t="n">
         <v>15.4</v>
@@ -4188,16 +4255,16 @@
         <v>20</v>
       </c>
       <c r="AA21" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>105.3</v>
+        <v>104.9</v>
       </c>
       <c r="AC21" t="n">
         <v>-2</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
         <v>17</v>
@@ -4206,19 +4273,19 @@
         <v>18</v>
       </c>
       <c r="AG21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH21" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI21" t="n">
         <v>3</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4230,7 +4297,7 @@
         <v>16</v>
       </c>
       <c r="AO21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP21" t="n">
         <v>28</v>
@@ -4245,13 +4312,13 @@
         <v>6</v>
       </c>
       <c r="AT21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW21" t="n">
         <v>18</v>
@@ -4263,7 +4330,7 @@
         <v>19</v>
       </c>
       <c r="AZ21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA21" t="n">
         <v>30</v>
@@ -4272,7 +4339,7 @@
         <v>3</v>
       </c>
       <c r="BC21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G22" t="n">
-        <v>0.077</v>
+        <v>0.08</v>
       </c>
       <c r="H22" t="n">
         <v>48</v>
@@ -4319,67 +4386,67 @@
         <v>35.6</v>
       </c>
       <c r="J22" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L22" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="M22" t="n">
         <v>10.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.37</v>
+        <v>0.375</v>
       </c>
       <c r="O22" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="P22" t="n">
         <v>24.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.754</v>
+        <v>0.761</v>
       </c>
       <c r="R22" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S22" t="n">
         <v>29.7</v>
       </c>
       <c r="T22" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U22" t="n">
-        <v>19.3</v>
+        <v>19</v>
       </c>
       <c r="V22" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="W22" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="AA22" t="n">
         <v>19.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>93.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC22" t="n">
         <v>-9.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>30</v>
@@ -4394,34 +4461,34 @@
         <v>24</v>
       </c>
       <c r="AI22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM22" t="n">
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AP22" t="n">
         <v>16</v>
       </c>
       <c r="AQ22" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AR22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AS22" t="n">
         <v>19</v>
@@ -4433,16 +4500,16 @@
         <v>26</v>
       </c>
       <c r="AV22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AW22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX22" t="n">
         <v>19</v>
       </c>
       <c r="AY22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ22" t="n">
         <v>19</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>5.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,16 +4640,16 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL23" t="n">
         <v>2</v>
@@ -4591,10 +4658,10 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP23" t="n">
         <v>5</v>
@@ -4609,19 +4676,19 @@
         <v>8</v>
       </c>
       <c r="AT23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU23" t="n">
         <v>27</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY23" t="n">
         <v>4</v>
@@ -4633,10 +4700,10 @@
         <v>6</v>
       </c>
       <c r="BB23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -4743,31 +4810,31 @@
         <v>-1.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF24" t="n">
         <v>19</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>18</v>
       </c>
       <c r="AG24" t="n">
         <v>20</v>
       </c>
       <c r="AH24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK24" t="n">
         <v>24</v>
       </c>
       <c r="AL24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM24" t="n">
         <v>29</v>
@@ -4776,10 +4843,10 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ24" t="n">
         <v>26</v>
@@ -4788,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="AS24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT24" t="n">
         <v>3</v>
@@ -4800,7 +4867,7 @@
         <v>25</v>
       </c>
       <c r="AW24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX24" t="n">
         <v>14</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -4925,40 +4992,40 @@
         <v>0.4</v>
       </c>
       <c r="AD25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI25" t="n">
         <v>5</v>
       </c>
-      <c r="AE25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>6</v>
-      </c>
       <c r="AJ25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN25" t="n">
         <v>5</v>
       </c>
       <c r="AO25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP25" t="n">
         <v>8</v>
@@ -4970,13 +5037,13 @@
         <v>28</v>
       </c>
       <c r="AS25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT25" t="n">
         <v>22</v>
       </c>
       <c r="AU25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AV25" t="n">
         <v>30</v>
@@ -4985,7 +5052,7 @@
         <v>25</v>
       </c>
       <c r="AX25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY25" t="n">
         <v>8</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -5032,130 +5099,130 @@
         <v>25</v>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>36.7</v>
+        <v>36.4</v>
       </c>
       <c r="J26" t="n">
-        <v>79.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.46</v>
+        <v>0.457</v>
       </c>
       <c r="L26" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M26" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="O26" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="P26" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="R26" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="S26" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>21</v>
+      </c>
+      <c r="V26" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="X26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AA26" t="n">
         <v>20.4</v>
       </c>
-      <c r="N26" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="O26" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="P26" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.782</v>
-      </c>
-      <c r="R26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="S26" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="T26" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="V26" t="n">
-        <v>13</v>
-      </c>
-      <c r="W26" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="X26" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>20.8</v>
-      </c>
       <c r="AB26" t="n">
-        <v>99.59999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
         <v>6</v>
       </c>
       <c r="AF26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AG26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AH26" t="n">
         <v>6</v>
       </c>
       <c r="AI26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ26" t="n">
         <v>17</v>
       </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AL26" t="n">
         <v>5</v>
       </c>
       <c r="AM26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO26" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AP26" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AR26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AU26" t="n">
         <v>13</v>
@@ -5167,22 +5234,22 @@
         <v>23</v>
       </c>
       <c r="AX26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY26" t="n">
         <v>1</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB26" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -5211,106 +5278,106 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" t="n">
         <v>7</v>
       </c>
       <c r="F27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G27" t="n">
-        <v>0.269</v>
+        <v>0.28</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37.2</v>
+        <v>37.8</v>
       </c>
       <c r="J27" t="n">
-        <v>81.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="K27" t="n">
-        <v>0.454</v>
+        <v>0.46</v>
       </c>
       <c r="L27" t="n">
         <v>5.2</v>
       </c>
       <c r="M27" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.304</v>
+        <v>0.301</v>
       </c>
       <c r="O27" t="n">
-        <v>18.1</v>
+        <v>17.8</v>
       </c>
       <c r="P27" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.776</v>
+        <v>0.773</v>
       </c>
       <c r="R27" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S27" t="n">
         <v>29.4</v>
       </c>
       <c r="T27" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="U27" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="V27" t="n">
         <v>15.7</v>
       </c>
       <c r="W27" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X27" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>97.7</v>
+        <v>98.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>-8.4</v>
+        <v>-7.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF27" t="n">
         <v>25</v>
       </c>
-      <c r="AF27" t="n">
-        <v>28</v>
-      </c>
       <c r="AG27" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK27" t="n">
         <v>9</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>13</v>
       </c>
       <c r="AL27" t="n">
         <v>24</v>
@@ -5322,16 +5389,16 @@
         <v>29</v>
       </c>
       <c r="AO27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP27" t="n">
         <v>23</v>
       </c>
-      <c r="AP27" t="n">
+      <c r="AQ27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR27" t="n">
         <v>22</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>24</v>
       </c>
       <c r="AS27" t="n">
         <v>21</v>
@@ -5340,28 +5407,28 @@
         <v>25</v>
       </c>
       <c r="AU27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX27" t="n">
         <v>23</v>
       </c>
-      <c r="AW27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>22</v>
-      </c>
       <c r="AY27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ27" t="n">
         <v>28</v>
       </c>
       <c r="BA27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -5474,13 +5541,13 @@
         <v>22</v>
       </c>
       <c r="AE28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG28" t="n">
         <v>6</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>7</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
@@ -5489,7 +5556,7 @@
         <v>13</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="n">
         <v>7</v>
@@ -5498,7 +5565,7 @@
         <v>4</v>
       </c>
       <c r="AM28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN28" t="n">
         <v>2</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
@@ -5525,7 +5592,7 @@
         <v>7</v>
       </c>
       <c r="AV28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW28" t="n">
         <v>30</v>
@@ -5546,7 +5613,7 @@
         <v>17</v>
       </c>
       <c r="BC28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -5653,22 +5720,22 @@
         <v>-3.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF29" t="n">
         <v>19</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>18</v>
       </c>
       <c r="AG29" t="n">
         <v>20</v>
       </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ29" t="n">
         <v>24</v>
@@ -5677,19 +5744,19 @@
         <v>17</v>
       </c>
       <c r="AL29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM29" t="n">
         <v>18</v>
       </c>
       <c r="AN29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5704,7 +5771,7 @@
         <v>29</v>
       </c>
       <c r="AU29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV29" t="n">
         <v>12</v>
@@ -5722,7 +5789,7 @@
         <v>3</v>
       </c>
       <c r="BA29" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BB29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF30" t="n">
         <v>14</v>
@@ -5850,7 +5917,7 @@
         <v>24</v>
       </c>
       <c r="AI30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ30" t="n">
         <v>23</v>
@@ -5865,7 +5932,7 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="n">
         <v>7</v>
@@ -5874,10 +5941,10 @@
         <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS30" t="n">
         <v>22</v>
@@ -5892,7 +5959,7 @@
         <v>29</v>
       </c>
       <c r="AW30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX30" t="n">
         <v>20</v>
@@ -5901,16 +5968,16 @@
         <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6096,7 @@
         <v>28</v>
       </c>
       <c r="AH31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI31" t="n">
         <v>12</v>
@@ -6047,22 +6114,22 @@
         <v>15</v>
       </c>
       <c r="AN31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO31" t="n">
         <v>19</v>
       </c>
       <c r="AP31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT31" t="n">
         <v>24</v>
@@ -6077,16 +6144,16 @@
         <v>12</v>
       </c>
       <c r="AX31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ31" t="n">
         <v>15</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>16</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-16-2008-09</t>
+          <t>2008-12-16</t>
         </is>
       </c>
     </row>
